--- a/data/2023-24/AHLdelegacije23-24.xlsx
+++ b/data/2023-24/AHLdelegacije23-24.xlsx
@@ -3,15 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8FADCF-1E87-451A-B6ED-2AE4DF725ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71C983B-6E47-4C2D-ABC6-54B41F88B0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AHL" sheetId="1" r:id="rId1"/>
     <sheet name="AHL_DAT" sheetId="3" r:id="rId2"/>
     <sheet name="AHL_DAT_STRING" sheetId="4" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1970,19 +1971,7 @@
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -2009,6 +1998,18 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2366,331 +2367,331 @@
   <sheetData>
     <row r="1" spans="1:82" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1">
-        <f>COUNTIF(A4:A50,"&lt;&gt;")</f>
+        <f t="shared" ref="A1:AF1" si="0">COUNTIF(A4:A50,"&lt;&gt;")</f>
         <v>38</v>
       </c>
       <c r="B1">
-        <f>COUNTIF(B4:B50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="C1">
-        <f>COUNTIF(C4:C50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="D1">
-        <f>COUNTIF(D4:D50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="E1">
-        <f>COUNTIF(E4:E50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="F1">
-        <f>COUNTIF(F4:F50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="G1">
-        <f>COUNTIF(G4:G50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="H1">
-        <f>COUNTIF(H4:H50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="I1">
-        <f>COUNTIF(I4:I50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="J1">
-        <f>COUNTIF(J4:J50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="K1">
-        <f>COUNTIF(K4:K50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="L1">
-        <f>COUNTIF(L4:L50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="M1">
-        <f>COUNTIF(M4:M50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="N1">
-        <f>COUNTIF(N4:N50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="O1">
-        <f>COUNTIF(O4:O50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="P1">
-        <f>COUNTIF(P4:P50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="Q1">
-        <f>COUNTIF(Q4:Q50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="R1">
-        <f>COUNTIF(R4:R50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="S1">
-        <f>COUNTIF(S4:S50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="T1">
-        <f>COUNTIF(T4:T50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="U1">
-        <f>COUNTIF(U4:U50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="V1">
-        <f>COUNTIF(V4:V50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="W1">
-        <f>COUNTIF(W4:W50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="X1">
-        <f>COUNTIF(X4:X50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="Y1">
-        <f>COUNTIF(Y4:Y50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="Z1">
-        <f>COUNTIF(Z4:Z50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="AA1">
-        <f>COUNTIF(AA4:AA50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="AB1">
-        <f>COUNTIF(AB4:AB50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="AC1">
-        <f>COUNTIF(AC4:AC50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="AD1">
-        <f>COUNTIF(AD4:AD50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="AE1">
-        <f>COUNTIF(AE4:AE50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="AF1">
-        <f>COUNTIF(AF4:AF50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="AG1">
-        <f>COUNTIF(AG4:AG50,"&lt;&gt;")</f>
+        <f t="shared" ref="AG1:BL1" si="1">COUNTIF(AG4:AG50,"&lt;&gt;")</f>
         <v>20</v>
       </c>
       <c r="AH1">
-        <f>COUNTIF(AH4:AH50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="AI1">
-        <f>COUNTIF(AI4:AI50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="AJ1">
-        <f>COUNTIF(AJ4:AJ50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="AK1">
-        <f>COUNTIF(AK4:AK50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="AL1">
-        <f>COUNTIF(AL4:AL50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="AM1">
-        <f>COUNTIF(AM4:AM50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="AN1">
-        <f>COUNTIF(AN4:AN50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="AO1">
-        <f>COUNTIF(AO4:AO50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="AP1">
-        <f>COUNTIF(AP4:AP50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="AQ1">
-        <f>COUNTIF(AQ4:AQ50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="AR1">
-        <f>COUNTIF(AR4:AR50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="AS1">
-        <f>COUNTIF(AS4:AS50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="AT1">
-        <f>COUNTIF(AT4:AT50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="AU1">
-        <f>COUNTIF(AU4:AU50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="AV1">
-        <f>COUNTIF(AV4:AV50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="AW1">
-        <f>COUNTIF(AW4:AW50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="AX1">
-        <f>COUNTIF(AX4:AX50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="AY1">
-        <f>COUNTIF(AY4:AY50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="AZ1">
-        <f>COUNTIF(AZ4:AZ50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="BA1">
-        <f>COUNTIF(BA4:BA50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="BB1">
-        <f>COUNTIF(BB4:BB50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="BC1">
-        <f>COUNTIF(BC4:BC50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="BD1">
-        <f>COUNTIF(BD4:BD50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="BE1">
-        <f>COUNTIF(BE4:BE50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="BF1">
-        <f>COUNTIF(BF4:BF50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="BG1">
-        <f>COUNTIF(BG4:BG50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="BH1">
-        <f>COUNTIF(BH4:BH50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="BI1">
-        <f>COUNTIF(BI4:BI50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="BJ1">
-        <f>COUNTIF(BJ4:BJ50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="BK1">
-        <f>COUNTIF(BK4:BK50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="BL1">
-        <f>COUNTIF(BL4:BL50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="BM1">
-        <f>COUNTIF(BM4:BM50,"&lt;&gt;")</f>
+        <f t="shared" ref="BM1:CD1" si="2">COUNTIF(BM4:BM50,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="BN1">
-        <f>COUNTIF(BN4:BN50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="BO1">
-        <f>COUNTIF(BO4:BO50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="BP1">
-        <f>COUNTIF(BP4:BP50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="BQ1">
-        <f>COUNTIF(BQ4:BQ50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="BR1">
-        <f>COUNTIF(BR4:BR50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="BS1">
-        <f>COUNTIF(BS4:BS50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="BT1">
-        <f>COUNTIF(BT4:BT50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="BU1">
-        <f>COUNTIF(BU4:BU50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="BV1">
-        <f>COUNTIF(BV4:BV50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="BW1">
-        <f>COUNTIF(BW4:BW50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="BX1">
-        <f>COUNTIF(BX4:BX50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="BY1">
-        <f>COUNTIF(BY4:BY50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="BZ1">
-        <f>COUNTIF(BZ4:BZ50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="CA1">
-        <f>COUNTIF(CA4:CA50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="CB1">
-        <f>COUNTIF(CB4:CB50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="CC1">
-        <f>COUNTIF(CC4:CC50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="CD1">
-        <f>COUNTIF(CD4:CD50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -13887,39 +13888,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="20" t="s">
         <v>544</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3">
+      <c r="B1" s="21"/>
+      <c r="C1" s="1">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
         <v>360</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="22" t="s">
         <v>545</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6">
+      <c r="B2" s="23"/>
+      <c r="C2" s="2">
         <f>C1*4</f>
         <v>1440</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="4">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
         <v>1438</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="6">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
         <v>208</v>
       </c>
@@ -13949,28 +13950,28 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="6">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
         <v>541</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="12">
         <v>2</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="13">
         <f>G5/16</f>
         <v>0.125</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="14">
         <f>(B4)/B3</f>
         <v>0.14464534075104313</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="8">
         <f>C2*H5</f>
         <v>180</v>
       </c>
@@ -13978,38 +13979,38 @@
         <f>B4</f>
         <v>208</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="9">
         <f>K5-J5</f>
         <v>28</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="10">
         <f>L5/4</f>
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="7" t="s">
         <v>548</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="6">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
         <v>689</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="15" t="s">
         <v>560</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="16">
         <v>7</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="17">
         <f>G6/16</f>
         <v>0.4375</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="18">
         <f>B5/B3</f>
         <v>0.37621696801112658</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="8">
         <f>C2*H6</f>
         <v>630</v>
       </c>
@@ -14017,31 +14018,31 @@
         <f>B5</f>
         <v>541</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="9">
         <f>K6-J6</f>
         <v>-89</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="10">
         <f>L6/4</f>
         <v>-22.25</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="15" t="s">
         <v>561</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="16">
         <v>7</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="17">
         <f>G7/16</f>
         <v>0.4375</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="18">
         <f>B6/B3</f>
         <v>0.47913769123783034</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="8">
         <f>C2*H7</f>
         <v>630</v>
       </c>
@@ -14049,11 +14050,11 @@
         <f>B6</f>
         <v>689</v>
       </c>
-      <c r="L7" s="23">
+      <c r="L7" s="19">
         <f>K7-J7</f>
         <v>59</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="10">
         <f>L7/4</f>
         <v>14.75</v>
       </c>
@@ -14074,4 +14075,13 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D9303CD-E1C8-4251-AF82-7A35E1AEE553}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>